--- a/medicamentos.xlsx
+++ b/medicamentos.xlsx
@@ -151,7 +151,10 @@
     <t xml:space="preserve">Nenhuma conhecida. </t>
   </si>
   <si>
-    <t xml:space="preserve">Não existem dados adequados sobre o uso de Duraphat 5000 500 mg/100 g Pasta dentífrica em mulheres grávidas. Estudos em animais revelaram toxicidade reprodutiva do fluoreto de sódio apenas quando administrado em níveis muito elevados. Em consequência, esta pasta dentífrica não deverá ser utilizada durante a gravidez e aleitamento a não ser que tenha sido efectuada uma cuidadosa avaliação benefício-risco. </t>
+    <t xml:space="preserve">Gravidez
+Não existem dados adequados sobre o uso de Duraphat 5000 500 mg/100 g Pasta dentífrica em mulheres grávidas. Estudos em animais revelaram toxicidade reprodutiva do fluoreto de sódio apenas quando administrado em níveis muito elevados. Em consequência, esta pasta dentífrica não deverá ser utilizada durante a gravidez e aleitamento a não ser que tenha sido efectuada uma cuidadosa avaliação benefício-risco. 
+Aleitamento
+Não existem dados adequados sobre o uso de Duraphat 5000 500 mg/100 g Pasta dentífrica em mulheres grávidas. Estudos em animais revelaram toxicidade reprodutiva do fluoreto de sódio apenas quando administrado em níveis muito elevados. Em consequência, esta pasta dentífrica não deverá ser utilizada durante a gravidez e aleitamento a não ser que tenha sido efectuada uma cuidadosa avaliação benefício-risco. </t>
   </si>
   <si>
     <t xml:space="preserve">Não relevante. </t>
@@ -6276,6 +6279,9 @@
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6285,9 +6291,6 @@
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
       <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -6980,7 +6983,7 @@
       <c r="J2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>44</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -7022,7 +7025,7 @@
       <c r="X2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="5" t="s">
         <v>58</v>
       </c>
       <c r="Z2" s="1" t="s">
@@ -7037,10 +7040,10 @@
       <c r="AC2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AD2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AD2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE2" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF2" s="1" t="s">
@@ -7060,10 +7063,10 @@
       <c r="A3" s="1">
         <v>8993709</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -7144,17 +7147,17 @@
       <c r="AC3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AD3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AD3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE3" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>92</v>
       </c>
       <c r="AG3" s="1"/>
-      <c r="AH3" s="7" t="s">
+      <c r="AH3" s="4" t="s">
         <v>93</v>
       </c>
       <c r="AI3" s="1" t="s">
@@ -7180,7 +7183,7 @@
       <c r="F4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>100</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -7198,10 +7201,10 @@
       <c r="L4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="4" t="s">
         <v>107</v>
       </c>
       <c r="O4" s="1" t="s">
@@ -7231,7 +7234,7 @@
       <c r="W4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="X4" s="4" t="s">
         <v>113</v>
       </c>
       <c r="Y4" s="1" t="s">
@@ -7249,19 +7252,19 @@
       <c r="AC4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF4" s="7" t="s">
+      <c r="AD4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF4" s="4" t="s">
         <v>119</v>
       </c>
       <c r="AG4" s="1">
         <v>12</v>
       </c>
-      <c r="AH4" s="7" t="s">
+      <c r="AH4" s="4" t="s">
         <v>120</v>
       </c>
       <c r="AI4" s="1" t="s">
@@ -7356,10 +7359,10 @@
       <c r="AC5" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="AD5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE5" s="5" t="s">
+      <c r="AD5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE5" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF5" s="1" t="s">
@@ -7461,10 +7464,10 @@
       <c r="AC6" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AD6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE6" s="5" t="s">
+      <c r="AD6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE6" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF6" s="1" t="s">
@@ -7497,7 +7500,7 @@
       <c r="F7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="4" t="s">
         <v>172</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -7566,10 +7569,10 @@
       <c r="AC7" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="AD7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE7" s="5" t="s">
+      <c r="AD7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE7" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF7" s="1" t="s">
@@ -7649,7 +7652,7 @@
       <c r="U8" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="V8" s="7" t="s">
+      <c r="V8" s="4" t="s">
         <v>198</v>
       </c>
       <c r="W8" s="1" t="s">
@@ -7673,10 +7676,10 @@
       <c r="AC8" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AD8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE8" s="5" t="s">
+      <c r="AD8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE8" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF8" s="1" t="s">
@@ -7780,10 +7783,10 @@
       <c r="AC9" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="AD9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE9" s="5" t="s">
+      <c r="AD9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE9" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF9" s="1" t="s">
@@ -7818,7 +7821,7 @@
       <c r="F10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="4" t="s">
         <v>236</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -7887,10 +7890,10 @@
       <c r="AC10" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AD10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE10" s="5" t="s">
+      <c r="AD10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE10" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF10" s="1" t="s">
@@ -7928,7 +7931,7 @@
       <c r="G11" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="4" t="s">
         <v>261</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -7970,7 +7973,7 @@
       <c r="U11" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="V11" s="7" t="s">
+      <c r="V11" s="4" t="s">
         <v>274</v>
       </c>
       <c r="W11" s="1" t="s">
@@ -7994,10 +7997,10 @@
       <c r="AC11" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="AD11" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE11" s="5" t="s">
+      <c r="AD11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE11" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF11" s="3" t="s">
@@ -8035,7 +8038,7 @@
       <c r="G12" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -8077,13 +8080,13 @@
       <c r="U12" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="V12" s="7" t="s">
+      <c r="V12" s="4" t="s">
         <v>302</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="X12" s="7" t="s">
+      <c r="X12" s="4" t="s">
         <v>304</v>
       </c>
       <c r="Y12" s="3" t="s">
@@ -8101,10 +8104,10 @@
       <c r="AC12" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="AD12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE12" s="5" t="s">
+      <c r="AD12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE12" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF12" s="3" t="s">
@@ -8140,7 +8143,7 @@
       <c r="G13" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="4" t="s">
         <v>318</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -8182,7 +8185,7 @@
       <c r="U13" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="V13" s="7" t="s">
+      <c r="V13" s="4" t="s">
         <v>325</v>
       </c>
       <c r="W13" s="12" t="s">
@@ -8206,10 +8209,10 @@
       <c r="AC13" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="AD13" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE13" s="5" t="s">
+      <c r="AD13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE13" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF13" s="3" t="s">
@@ -8313,10 +8316,10 @@
       <c r="AC14" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="AD14" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE14" s="5" t="s">
+      <c r="AD14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE14" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF14" s="13" t="s">
@@ -8369,7 +8372,7 @@
       <c r="L15" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="4" t="s">
         <v>367</v>
       </c>
       <c r="N15" s="13" t="s">
@@ -8420,10 +8423,10 @@
       <c r="AC15" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="AD15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE15" s="5" t="s">
+      <c r="AD15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE15" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF15" s="13" t="s">
@@ -8476,7 +8479,7 @@
       <c r="L16" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="4" t="s">
         <v>391</v>
       </c>
       <c r="N16" s="13" t="s">
@@ -8527,10 +8530,10 @@
       <c r="AC16" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="AD16" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE16" s="5" t="s">
+      <c r="AD16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE16" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF16" s="13" t="s">
@@ -8634,10 +8637,10 @@
       <c r="AC17" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE17" s="5" t="s">
+      <c r="AD17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE17" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF17" s="1" t="s">
@@ -8741,10 +8744,10 @@
       <c r="AC18" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE18" s="5" t="s">
+      <c r="AD18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE18" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF18" s="1" t="s">
@@ -8848,10 +8851,10 @@
       <c r="AC19" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE19" s="5" t="s">
+      <c r="AD19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE19" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF19" s="1" t="s">
@@ -8955,10 +8958,10 @@
       <c r="AC20" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE20" s="5" t="s">
+      <c r="AD20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE20" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF20" s="1" t="s">
@@ -9062,10 +9065,10 @@
       <c r="AC21" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE21" s="5" t="s">
+      <c r="AD21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE21" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF21" s="1" t="s">
@@ -9169,10 +9172,10 @@
       <c r="AC22" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE22" s="5" t="s">
+      <c r="AD22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE22" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF22" s="1" t="s">
@@ -9276,10 +9279,10 @@
       <c r="AC23" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE23" s="5" t="s">
+      <c r="AD23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE23" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF23" s="1" t="s">
@@ -9383,10 +9386,10 @@
       <c r="AC24" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE24" s="5" t="s">
+      <c r="AD24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE24" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF24" s="1" t="s">
@@ -9490,10 +9493,10 @@
       <c r="AC25" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD25" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE25" s="5" t="s">
+      <c r="AD25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE25" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF25" s="1" t="s">
@@ -9597,10 +9600,10 @@
       <c r="AC26" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD26" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE26" s="5" t="s">
+      <c r="AD26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE26" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF26" s="1" t="s">
@@ -9704,10 +9707,10 @@
       <c r="AC27" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE27" s="5" t="s">
+      <c r="AD27" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE27" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF27" s="1" t="s">
@@ -9811,10 +9814,10 @@
       <c r="AC28" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE28" s="5" t="s">
+      <c r="AD28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE28" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF28" s="1" t="s">
@@ -9918,10 +9921,10 @@
       <c r="AC29" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD29" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE29" s="5" t="s">
+      <c r="AD29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE29" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF29" s="1" t="s">
@@ -10025,10 +10028,10 @@
       <c r="AC30" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD30" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE30" s="5" t="s">
+      <c r="AD30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE30" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF30" s="1" t="s">
@@ -10132,10 +10135,10 @@
       <c r="AC31" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD31" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE31" s="5" t="s">
+      <c r="AD31" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE31" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF31" s="1" t="s">
@@ -10155,16 +10158,16 @@
       <c r="A32" s="1">
         <v>9999999</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="4" t="s">
         <v>438</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -10239,10 +10242,10 @@
       <c r="AC32" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD32" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE32" s="5" t="s">
+      <c r="AD32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE32" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF32" s="1" t="s">
@@ -10262,16 +10265,16 @@
       <c r="A33" s="1">
         <v>9999999</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="4" t="s">
         <v>445</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -10346,10 +10349,10 @@
       <c r="AC33" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD33" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE33" s="5" t="s">
+      <c r="AD33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE33" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF33" s="1" t="s">
@@ -10453,10 +10456,10 @@
       <c r="AC34" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE34" s="5" t="s">
+      <c r="AD34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE34" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF34" s="1" t="s">
@@ -10560,10 +10563,10 @@
       <c r="AC35" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD35" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE35" s="5" t="s">
+      <c r="AD35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE35" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF35" s="1" t="s">
@@ -10667,10 +10670,10 @@
       <c r="AC36" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD36" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE36" s="5" t="s">
+      <c r="AD36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE36" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF36" s="1" t="s">
@@ -10774,10 +10777,10 @@
       <c r="AC37" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD37" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE37" s="5" t="s">
+      <c r="AD37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE37" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF37" s="1" t="s">
@@ -10881,10 +10884,10 @@
       <c r="AC38" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD38" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE38" s="5" t="s">
+      <c r="AD38" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE38" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF38" s="1" t="s">
@@ -10988,10 +10991,10 @@
       <c r="AC39" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD39" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE39" s="5" t="s">
+      <c r="AD39" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE39" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF39" s="1" t="s">
@@ -11095,10 +11098,10 @@
       <c r="AC40" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE40" s="5" t="s">
+      <c r="AD40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE40" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF40" s="1" t="s">
@@ -11202,10 +11205,10 @@
       <c r="AC41" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD41" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE41" s="5" t="s">
+      <c r="AD41" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE41" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF41" s="1" t="s">
@@ -11309,10 +11312,10 @@
       <c r="AC42" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD42" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE42" s="5" t="s">
+      <c r="AD42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE42" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF42" s="1" t="s">
@@ -11416,10 +11419,10 @@
       <c r="AC43" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD43" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE43" s="5" t="s">
+      <c r="AD43" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE43" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF43" s="1" t="s">
@@ -11523,10 +11526,10 @@
       <c r="AC44" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD44" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE44" s="5" t="s">
+      <c r="AD44" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE44" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF44" s="1" t="s">
@@ -11630,10 +11633,10 @@
       <c r="AC45" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD45" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE45" s="5" t="s">
+      <c r="AD45" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE45" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF45" s="1" t="s">
@@ -11737,10 +11740,10 @@
       <c r="AC46" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD46" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE46" s="5" t="s">
+      <c r="AD46" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE46" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF46" s="1" t="s">
@@ -11844,10 +11847,10 @@
       <c r="AC47" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD47" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE47" s="5" t="s">
+      <c r="AD47" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE47" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF47" s="1" t="s">
@@ -11951,10 +11954,10 @@
       <c r="AC48" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD48" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE48" s="5" t="s">
+      <c r="AD48" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE48" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF48" s="1" t="s">
@@ -12058,10 +12061,10 @@
       <c r="AC49" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD49" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE49" s="5" t="s">
+      <c r="AD49" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE49" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF49" s="1" t="s">
@@ -12165,10 +12168,10 @@
       <c r="AC50" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD50" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE50" s="5" t="s">
+      <c r="AD50" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE50" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF50" s="1" t="s">
@@ -12272,10 +12275,10 @@
       <c r="AC51" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD51" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE51" s="5" t="s">
+      <c r="AD51" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE51" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF51" s="1" t="s">
@@ -12379,10 +12382,10 @@
       <c r="AC52" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD52" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE52" s="5" t="s">
+      <c r="AD52" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE52" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF52" s="1" t="s">
@@ -12486,10 +12489,10 @@
       <c r="AC53" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD53" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE53" s="5" t="s">
+      <c r="AD53" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE53" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF53" s="1" t="s">
@@ -12593,10 +12596,10 @@
       <c r="AC54" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD54" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE54" s="5" t="s">
+      <c r="AD54" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE54" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF54" s="1" t="s">
@@ -12649,7 +12652,7 @@
       <c r="L55" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="M55" s="7" t="s">
+      <c r="M55" s="4" t="s">
         <v>518</v>
       </c>
       <c r="N55" s="1" t="s">
@@ -12685,7 +12688,7 @@
       <c r="X55" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="Y55" s="7" t="s">
+      <c r="Y55" s="4" t="s">
         <v>526</v>
       </c>
       <c r="Z55" s="1" t="s">
@@ -12700,10 +12703,10 @@
       <c r="AC55" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="AD55" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE55" s="5" t="s">
+      <c r="AD55" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE55" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF55" s="1" t="s">
@@ -12807,10 +12810,10 @@
       <c r="AC56" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD56" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE56" s="5" t="s">
+      <c r="AD56" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE56" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF56" s="1" t="s">
@@ -12914,10 +12917,10 @@
       <c r="AC57" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD57" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE57" s="5" t="s">
+      <c r="AD57" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE57" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF57" s="1" t="s">
@@ -13021,10 +13024,10 @@
       <c r="AC58" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD58" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE58" s="5" t="s">
+      <c r="AD58" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE58" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF58" s="1" t="s">
@@ -13128,10 +13131,10 @@
       <c r="AC59" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD59" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE59" s="5" t="s">
+      <c r="AD59" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE59" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF59" s="1" t="s">
@@ -13235,10 +13238,10 @@
       <c r="AC60" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD60" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE60" s="5" t="s">
+      <c r="AD60" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE60" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF60" s="1" t="s">
@@ -13342,10 +13345,10 @@
       <c r="AC61" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD61" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE61" s="5" t="s">
+      <c r="AD61" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE61" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF61" s="1" t="s">
@@ -13449,10 +13452,10 @@
       <c r="AC62" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD62" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE62" s="5" t="s">
+      <c r="AD62" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE62" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF62" s="1" t="s">
@@ -13556,10 +13559,10 @@
       <c r="AC63" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD63" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE63" s="5" t="s">
+      <c r="AD63" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE63" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF63" s="1" t="s">
@@ -13663,10 +13666,10 @@
       <c r="AC64" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD64" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE64" s="5" t="s">
+      <c r="AD64" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE64" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF64" s="1" t="s">
@@ -13770,10 +13773,10 @@
       <c r="AC65" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD65" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE65" s="5" t="s">
+      <c r="AD65" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE65" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF65" s="1" t="s">
@@ -13877,10 +13880,10 @@
       <c r="AC66" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD66" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE66" s="5" t="s">
+      <c r="AD66" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE66" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF66" s="1" t="s">
@@ -13984,10 +13987,10 @@
       <c r="AC67" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD67" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE67" s="5" t="s">
+      <c r="AD67" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE67" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF67" s="1" t="s">
@@ -14091,10 +14094,10 @@
       <c r="AC68" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD68" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE68" s="5" t="s">
+      <c r="AD68" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE68" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF68" s="1" t="s">
@@ -14198,10 +14201,10 @@
       <c r="AC69" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD69" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE69" s="5" t="s">
+      <c r="AD69" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE69" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF69" s="1" t="s">
@@ -14305,10 +14308,10 @@
       <c r="AC70" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD70" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE70" s="5" t="s">
+      <c r="AD70" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE70" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF70" s="1" t="s">
@@ -14412,10 +14415,10 @@
       <c r="AC71" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD71" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE71" s="5" t="s">
+      <c r="AD71" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE71" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF71" s="1" t="s">
@@ -14519,10 +14522,10 @@
       <c r="AC72" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD72" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE72" s="5" t="s">
+      <c r="AD72" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE72" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF72" s="1" t="s">
@@ -14626,10 +14629,10 @@
       <c r="AC73" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD73" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE73" s="5" t="s">
+      <c r="AD73" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE73" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF73" s="1" t="s">
@@ -14733,10 +14736,10 @@
       <c r="AC74" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD74" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE74" s="5" t="s">
+      <c r="AD74" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE74" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF74" s="1" t="s">
@@ -14840,10 +14843,10 @@
       <c r="AC75" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD75" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE75" s="5" t="s">
+      <c r="AD75" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE75" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF75" s="1" t="s">
@@ -14947,10 +14950,10 @@
       <c r="AC76" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD76" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE76" s="5" t="s">
+      <c r="AD76" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE76" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF76" s="1" t="s">
@@ -15054,10 +15057,10 @@
       <c r="AC77" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD77" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE77" s="5" t="s">
+      <c r="AD77" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE77" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF77" s="1" t="s">
@@ -15161,10 +15164,10 @@
       <c r="AC78" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD78" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE78" s="5" t="s">
+      <c r="AD78" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE78" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF78" s="1" t="s">
@@ -15268,10 +15271,10 @@
       <c r="AC79" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD79" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE79" s="5" t="s">
+      <c r="AD79" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE79" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF79" s="1" t="s">
@@ -15375,10 +15378,10 @@
       <c r="AC80" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD80" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE80" s="5" t="s">
+      <c r="AD80" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE80" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF80" s="1" t="s">
@@ -15482,10 +15485,10 @@
       <c r="AC81" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD81" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE81" s="5" t="s">
+      <c r="AD81" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE81" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF81" s="1" t="s">
@@ -15589,10 +15592,10 @@
       <c r="AC82" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD82" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE82" s="5" t="s">
+      <c r="AD82" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE82" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF82" s="1" t="s">
@@ -15696,10 +15699,10 @@
       <c r="AC83" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD83" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE83" s="5" t="s">
+      <c r="AD83" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE83" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF83" s="1" t="s">
@@ -15803,10 +15806,10 @@
       <c r="AC84" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD84" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE84" s="5" t="s">
+      <c r="AD84" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE84" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF84" s="1" t="s">
@@ -15826,16 +15829,16 @@
       <c r="A85" s="1">
         <v>9999999</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="4" t="s">
         <v>621</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -15910,10 +15913,10 @@
       <c r="AC85" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD85" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE85" s="5" t="s">
+      <c r="AD85" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE85" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF85" s="1" t="s">
@@ -16017,10 +16020,10 @@
       <c r="AC86" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD86" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE86" s="5" t="s">
+      <c r="AD86" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE86" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF86" s="1" t="s">
@@ -16124,10 +16127,10 @@
       <c r="AC87" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD87" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE87" s="5" t="s">
+      <c r="AD87" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE87" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF87" s="1" t="s">
@@ -16231,10 +16234,10 @@
       <c r="AC88" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD88" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE88" s="5" t="s">
+      <c r="AD88" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE88" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF88" s="1" t="s">
@@ -16338,10 +16341,10 @@
       <c r="AC89" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD89" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE89" s="5" t="s">
+      <c r="AD89" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE89" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF89" s="1" t="s">
@@ -16445,10 +16448,10 @@
       <c r="AC90" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD90" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE90" s="5" t="s">
+      <c r="AD90" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE90" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF90" s="1" t="s">
@@ -16552,10 +16555,10 @@
       <c r="AC91" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD91" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE91" s="5" t="s">
+      <c r="AD91" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE91" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF91" s="1" t="s">
@@ -16659,10 +16662,10 @@
       <c r="AC92" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD92" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE92" s="5" t="s">
+      <c r="AD92" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE92" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF92" s="1" t="s">
@@ -16766,10 +16769,10 @@
       <c r="AC93" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD93" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE93" s="5" t="s">
+      <c r="AD93" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE93" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF93" s="1" t="s">
@@ -16873,10 +16876,10 @@
       <c r="AC94" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD94" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE94" s="5" t="s">
+      <c r="AD94" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE94" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF94" s="1" t="s">
@@ -16980,10 +16983,10 @@
       <c r="AC95" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD95" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE95" s="5" t="s">
+      <c r="AD95" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE95" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF95" s="1" t="s">
@@ -17087,10 +17090,10 @@
       <c r="AC96" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD96" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE96" s="5" t="s">
+      <c r="AD96" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE96" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF96" s="1" t="s">
@@ -17194,10 +17197,10 @@
       <c r="AC97" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD97" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE97" s="5" t="s">
+      <c r="AD97" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE97" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF97" s="1" t="s">
@@ -17301,10 +17304,10 @@
       <c r="AC98" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD98" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE98" s="5" t="s">
+      <c r="AD98" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE98" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF98" s="1" t="s">
@@ -17408,10 +17411,10 @@
       <c r="AC99" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD99" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE99" s="5" t="s">
+      <c r="AD99" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE99" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF99" s="1" t="s">
@@ -17515,10 +17518,10 @@
       <c r="AC100" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD100" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE100" s="5" t="s">
+      <c r="AD100" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE100" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF100" s="1" t="s">
@@ -17622,10 +17625,10 @@
       <c r="AC101" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD101" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE101" s="5" t="s">
+      <c r="AD101" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE101" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF101" s="1" t="s">
@@ -17729,10 +17732,10 @@
       <c r="AC102" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD102" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE102" s="5" t="s">
+      <c r="AD102" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE102" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF102" s="1" t="s">
@@ -17836,10 +17839,10 @@
       <c r="AC103" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD103" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE103" s="5" t="s">
+      <c r="AD103" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE103" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF103" s="1" t="s">
@@ -17943,10 +17946,10 @@
       <c r="AC104" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD104" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE104" s="5" t="s">
+      <c r="AD104" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE104" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF104" s="1" t="s">
@@ -18050,10 +18053,10 @@
       <c r="AC105" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD105" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE105" s="5" t="s">
+      <c r="AD105" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE105" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF105" s="1" t="s">
@@ -18157,10 +18160,10 @@
       <c r="AC106" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD106" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE106" s="5" t="s">
+      <c r="AD106" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE106" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF106" s="1" t="s">
@@ -18264,10 +18267,10 @@
       <c r="AC107" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD107" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE107" s="5" t="s">
+      <c r="AD107" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE107" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF107" s="1" t="s">
@@ -18371,10 +18374,10 @@
       <c r="AC108" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD108" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE108" s="5" t="s">
+      <c r="AD108" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE108" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF108" s="1" t="s">
@@ -18478,10 +18481,10 @@
       <c r="AC109" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD109" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE109" s="5" t="s">
+      <c r="AD109" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE109" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF109" s="1" t="s">
@@ -18585,10 +18588,10 @@
       <c r="AC110" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD110" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE110" s="5" t="s">
+      <c r="AD110" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE110" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF110" s="1" t="s">
@@ -18692,10 +18695,10 @@
       <c r="AC111" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD111" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE111" s="5" t="s">
+      <c r="AD111" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE111" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF111" s="1" t="s">
@@ -18799,10 +18802,10 @@
       <c r="AC112" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD112" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE112" s="5" t="s">
+      <c r="AD112" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE112" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF112" s="1" t="s">
@@ -18906,10 +18909,10 @@
       <c r="AC113" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD113" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE113" s="5" t="s">
+      <c r="AD113" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE113" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF113" s="1" t="s">
@@ -19013,10 +19016,10 @@
       <c r="AC114" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD114" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE114" s="5" t="s">
+      <c r="AD114" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE114" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF114" s="1" t="s">
@@ -19120,10 +19123,10 @@
       <c r="AC115" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD115" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE115" s="5" t="s">
+      <c r="AD115" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE115" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF115" s="1" t="s">
@@ -19227,10 +19230,10 @@
       <c r="AC116" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD116" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE116" s="5" t="s">
+      <c r="AD116" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE116" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF116" s="1" t="s">
@@ -19334,10 +19337,10 @@
       <c r="AC117" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD117" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE117" s="5" t="s">
+      <c r="AD117" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE117" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF117" s="1" t="s">
@@ -19441,10 +19444,10 @@
       <c r="AC118" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD118" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE118" s="5" t="s">
+      <c r="AD118" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE118" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF118" s="1" t="s">
@@ -19548,10 +19551,10 @@
       <c r="AC119" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD119" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE119" s="5" t="s">
+      <c r="AD119" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE119" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF119" s="1" t="s">
@@ -19655,10 +19658,10 @@
       <c r="AC120" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD120" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE120" s="5" t="s">
+      <c r="AD120" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE120" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF120" s="1" t="s">
@@ -19762,10 +19765,10 @@
       <c r="AC121" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD121" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE121" s="5" t="s">
+      <c r="AD121" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE121" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF121" s="1" t="s">
@@ -19869,10 +19872,10 @@
       <c r="AC122" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD122" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE122" s="5" t="s">
+      <c r="AD122" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE122" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF122" s="1" t="s">
@@ -19976,10 +19979,10 @@
       <c r="AC123" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD123" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE123" s="5" t="s">
+      <c r="AD123" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE123" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF123" s="1" t="s">
@@ -20083,10 +20086,10 @@
       <c r="AC124" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD124" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE124" s="5" t="s">
+      <c r="AD124" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE124" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF124" s="1" t="s">
@@ -20190,10 +20193,10 @@
       <c r="AC125" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD125" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE125" s="5" t="s">
+      <c r="AD125" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE125" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF125" s="1" t="s">
@@ -20297,10 +20300,10 @@
       <c r="AC126" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD126" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE126" s="5" t="s">
+      <c r="AD126" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE126" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF126" s="1" t="s">
@@ -20404,10 +20407,10 @@
       <c r="AC127" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD127" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE127" s="5" t="s">
+      <c r="AD127" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE127" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF127" s="1" t="s">
@@ -20511,10 +20514,10 @@
       <c r="AC128" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD128" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE128" s="5" t="s">
+      <c r="AD128" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE128" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF128" s="1" t="s">
@@ -20618,10 +20621,10 @@
       <c r="AC129" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD129" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE129" s="5" t="s">
+      <c r="AD129" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE129" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF129" s="1" t="s">
@@ -20725,10 +20728,10 @@
       <c r="AC130" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD130" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE130" s="5" t="s">
+      <c r="AD130" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE130" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF130" s="1" t="s">
@@ -20832,10 +20835,10 @@
       <c r="AC131" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD131" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE131" s="5" t="s">
+      <c r="AD131" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE131" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF131" s="1" t="s">
@@ -20939,10 +20942,10 @@
       <c r="AC132" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD132" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE132" s="5" t="s">
+      <c r="AD132" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE132" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF132" s="1" t="s">
@@ -21046,10 +21049,10 @@
       <c r="AC133" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD133" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE133" s="5" t="s">
+      <c r="AD133" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE133" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF133" s="1" t="s">
@@ -21153,10 +21156,10 @@
       <c r="AC134" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD134" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE134" s="5" t="s">
+      <c r="AD134" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF134" s="1" t="s">
@@ -21260,10 +21263,10 @@
       <c r="AC135" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD135" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE135" s="5" t="s">
+      <c r="AD135" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE135" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF135" s="1" t="s">
@@ -21367,10 +21370,10 @@
       <c r="AC136" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD136" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE136" s="5" t="s">
+      <c r="AD136" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE136" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF136" s="1" t="s">
@@ -21474,10 +21477,10 @@
       <c r="AC137" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD137" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE137" s="5" t="s">
+      <c r="AD137" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE137" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF137" s="1" t="s">
@@ -21581,10 +21584,10 @@
       <c r="AC138" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD138" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE138" s="5" t="s">
+      <c r="AD138" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE138" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF138" s="1" t="s">
@@ -21688,10 +21691,10 @@
       <c r="AC139" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD139" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE139" s="5" t="s">
+      <c r="AD139" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE139" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF139" s="1" t="s">
@@ -21795,10 +21798,10 @@
       <c r="AC140" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD140" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE140" s="5" t="s">
+      <c r="AD140" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE140" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF140" s="1" t="s">
@@ -21902,10 +21905,10 @@
       <c r="AC141" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD141" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE141" s="5" t="s">
+      <c r="AD141" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE141" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF141" s="1" t="s">
@@ -22009,10 +22012,10 @@
       <c r="AC142" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD142" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE142" s="5" t="s">
+      <c r="AD142" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE142" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF142" s="1" t="s">
@@ -22116,10 +22119,10 @@
       <c r="AC143" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD143" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE143" s="5" t="s">
+      <c r="AD143" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE143" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF143" s="1" t="s">
@@ -22223,10 +22226,10 @@
       <c r="AC144" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD144" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE144" s="5" t="s">
+      <c r="AD144" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE144" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF144" s="1" t="s">
@@ -22330,10 +22333,10 @@
       <c r="AC145" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD145" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE145" s="5" t="s">
+      <c r="AD145" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE145" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF145" s="1" t="s">
@@ -22437,10 +22440,10 @@
       <c r="AC146" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD146" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE146" s="5" t="s">
+      <c r="AD146" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE146" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF146" s="1" t="s">
@@ -22544,10 +22547,10 @@
       <c r="AC147" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD147" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE147" s="5" t="s">
+      <c r="AD147" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE147" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF147" s="1" t="s">
@@ -22651,10 +22654,10 @@
       <c r="AC148" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD148" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE148" s="5" t="s">
+      <c r="AD148" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE148" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF148" s="1" t="s">
@@ -22758,10 +22761,10 @@
       <c r="AC149" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD149" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE149" s="5" t="s">
+      <c r="AD149" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE149" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF149" s="1" t="s">
@@ -22865,10 +22868,10 @@
       <c r="AC150" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD150" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE150" s="5" t="s">
+      <c r="AD150" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE150" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF150" s="1" t="s">
@@ -22972,10 +22975,10 @@
       <c r="AC151" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD151" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE151" s="5" t="s">
+      <c r="AD151" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE151" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF151" s="1" t="s">
@@ -23079,10 +23082,10 @@
       <c r="AC152" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD152" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE152" s="5" t="s">
+      <c r="AD152" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF152" s="1" t="s">
@@ -23186,10 +23189,10 @@
       <c r="AC153" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD153" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE153" s="5" t="s">
+      <c r="AD153" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE153" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF153" s="1" t="s">
@@ -23293,10 +23296,10 @@
       <c r="AC154" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD154" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE154" s="5" t="s">
+      <c r="AD154" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE154" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF154" s="1" t="s">
@@ -23400,10 +23403,10 @@
       <c r="AC155" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD155" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE155" s="5" t="s">
+      <c r="AD155" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE155" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF155" s="1" t="s">
@@ -23507,10 +23510,10 @@
       <c r="AC156" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD156" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE156" s="5" t="s">
+      <c r="AD156" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE156" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF156" s="1" t="s">
@@ -23614,10 +23617,10 @@
       <c r="AC157" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD157" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE157" s="5" t="s">
+      <c r="AD157" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE157" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF157" s="1" t="s">
@@ -23721,10 +23724,10 @@
       <c r="AC158" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD158" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE158" s="5" t="s">
+      <c r="AD158" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE158" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF158" s="1" t="s">
@@ -23828,10 +23831,10 @@
       <c r="AC159" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD159" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE159" s="5" t="s">
+      <c r="AD159" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE159" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF159" s="1" t="s">
@@ -23935,10 +23938,10 @@
       <c r="AC160" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD160" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE160" s="5" t="s">
+      <c r="AD160" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE160" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF160" s="1" t="s">
@@ -24042,10 +24045,10 @@
       <c r="AC161" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD161" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE161" s="5" t="s">
+      <c r="AD161" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE161" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF161" s="1" t="s">
@@ -24149,10 +24152,10 @@
       <c r="AC162" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD162" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE162" s="5" t="s">
+      <c r="AD162" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE162" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF162" s="1" t="s">
@@ -24256,10 +24259,10 @@
       <c r="AC163" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD163" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE163" s="5" t="s">
+      <c r="AD163" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE163" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF163" s="1" t="s">
@@ -24363,10 +24366,10 @@
       <c r="AC164" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD164" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE164" s="5" t="s">
+      <c r="AD164" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE164" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF164" s="1" t="s">
@@ -24470,10 +24473,10 @@
       <c r="AC165" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD165" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE165" s="5" t="s">
+      <c r="AD165" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE165" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF165" s="1" t="s">
@@ -24577,10 +24580,10 @@
       <c r="AC166" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD166" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE166" s="5" t="s">
+      <c r="AD166" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE166" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF166" s="1" t="s">
@@ -24684,10 +24687,10 @@
       <c r="AC167" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD167" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE167" s="5" t="s">
+      <c r="AD167" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE167" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF167" s="1" t="s">
@@ -24791,10 +24794,10 @@
       <c r="AC168" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD168" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE168" s="5" t="s">
+      <c r="AD168" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE168" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF168" s="1" t="s">
@@ -24898,10 +24901,10 @@
       <c r="AC169" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD169" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE169" s="5" t="s">
+      <c r="AD169" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE169" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF169" s="1" t="s">
@@ -25005,10 +25008,10 @@
       <c r="AC170" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD170" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE170" s="5" t="s">
+      <c r="AD170" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE170" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF170" s="1" t="s">
@@ -25112,10 +25115,10 @@
       <c r="AC171" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD171" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE171" s="5" t="s">
+      <c r="AD171" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE171" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF171" s="1" t="s">
@@ -25219,10 +25222,10 @@
       <c r="AC172" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD172" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE172" s="5" t="s">
+      <c r="AD172" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE172" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF172" s="1" t="s">
@@ -25326,10 +25329,10 @@
       <c r="AC173" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD173" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE173" s="5" t="s">
+      <c r="AD173" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE173" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF173" s="1" t="s">
@@ -25433,10 +25436,10 @@
       <c r="AC174" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD174" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE174" s="5" t="s">
+      <c r="AD174" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE174" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF174" s="1" t="s">
@@ -25540,10 +25543,10 @@
       <c r="AC175" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD175" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE175" s="5" t="s">
+      <c r="AD175" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE175" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF175" s="1" t="s">
@@ -25647,10 +25650,10 @@
       <c r="AC176" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD176" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE176" s="5" t="s">
+      <c r="AD176" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE176" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF176" s="1" t="s">
@@ -25754,10 +25757,10 @@
       <c r="AC177" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD177" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE177" s="5" t="s">
+      <c r="AD177" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE177" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF177" s="1" t="s">
@@ -25861,10 +25864,10 @@
       <c r="AC178" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD178" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE178" s="5" t="s">
+      <c r="AD178" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE178" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF178" s="1" t="s">
@@ -25968,10 +25971,10 @@
       <c r="AC179" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD179" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE179" s="5" t="s">
+      <c r="AD179" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE179" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF179" s="1" t="s">
@@ -26075,10 +26078,10 @@
       <c r="AC180" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD180" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE180" s="5" t="s">
+      <c r="AD180" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE180" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF180" s="1" t="s">
@@ -26182,10 +26185,10 @@
       <c r="AC181" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD181" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE181" s="5" t="s">
+      <c r="AD181" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE181" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF181" s="1" t="s">
@@ -26289,10 +26292,10 @@
       <c r="AC182" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD182" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE182" s="5" t="s">
+      <c r="AD182" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE182" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF182" s="1" t="s">
@@ -26396,10 +26399,10 @@
       <c r="AC183" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD183" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE183" s="5" t="s">
+      <c r="AD183" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE183" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF183" s="1" t="s">
@@ -26503,10 +26506,10 @@
       <c r="AC184" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD184" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE184" s="5" t="s">
+      <c r="AD184" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE184" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF184" s="1" t="s">
@@ -26610,10 +26613,10 @@
       <c r="AC185" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD185" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE185" s="5" t="s">
+      <c r="AD185" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE185" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF185" s="1" t="s">
@@ -26717,10 +26720,10 @@
       <c r="AC186" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD186" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE186" s="5" t="s">
+      <c r="AD186" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE186" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF186" s="1" t="s">
@@ -26824,10 +26827,10 @@
       <c r="AC187" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD187" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE187" s="5" t="s">
+      <c r="AD187" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE187" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF187" s="1" t="s">
@@ -26931,10 +26934,10 @@
       <c r="AC188" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD188" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE188" s="5" t="s">
+      <c r="AD188" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE188" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF188" s="1" t="s">
@@ -27038,10 +27041,10 @@
       <c r="AC189" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD189" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE189" s="5" t="s">
+      <c r="AD189" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE189" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF189" s="1" t="s">
@@ -27145,10 +27148,10 @@
       <c r="AC190" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD190" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE190" s="5" t="s">
+      <c r="AD190" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE190" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF190" s="1" t="s">
@@ -27252,10 +27255,10 @@
       <c r="AC191" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD191" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE191" s="5" t="s">
+      <c r="AD191" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE191" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF191" s="1" t="s">
@@ -27359,10 +27362,10 @@
       <c r="AC192" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD192" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE192" s="5" t="s">
+      <c r="AD192" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE192" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF192" s="1" t="s">
@@ -27466,10 +27469,10 @@
       <c r="AC193" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD193" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE193" s="5" t="s">
+      <c r="AD193" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE193" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF193" s="1" t="s">
@@ -27573,10 +27576,10 @@
       <c r="AC194" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD194" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE194" s="5" t="s">
+      <c r="AD194" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE194" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF194" s="1" t="s">
@@ -27680,10 +27683,10 @@
       <c r="AC195" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD195" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE195" s="5" t="s">
+      <c r="AD195" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE195" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF195" s="1" t="s">
@@ -27787,10 +27790,10 @@
       <c r="AC196" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD196" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE196" s="5" t="s">
+      <c r="AD196" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE196" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF196" s="1" t="s">
@@ -27894,10 +27897,10 @@
       <c r="AC197" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD197" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE197" s="5" t="s">
+      <c r="AD197" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE197" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF197" s="1" t="s">
@@ -28001,10 +28004,10 @@
       <c r="AC198" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD198" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE198" s="5" t="s">
+      <c r="AD198" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE198" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF198" s="1" t="s">
@@ -28108,10 +28111,10 @@
       <c r="AC199" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD199" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE199" s="5" t="s">
+      <c r="AD199" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE199" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF199" s="1" t="s">
@@ -28215,10 +28218,10 @@
       <c r="AC200" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD200" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE200" s="5" t="s">
+      <c r="AD200" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE200" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF200" s="1" t="s">
@@ -28322,10 +28325,10 @@
       <c r="AC201" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD201" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE201" s="5" t="s">
+      <c r="AD201" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE201" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF201" s="1" t="s">
@@ -28429,10 +28432,10 @@
       <c r="AC202" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD202" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE202" s="5" t="s">
+      <c r="AD202" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE202" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF202" s="1" t="s">
@@ -28536,10 +28539,10 @@
       <c r="AC203" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD203" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE203" s="5" t="s">
+      <c r="AD203" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE203" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF203" s="1" t="s">
@@ -28643,10 +28646,10 @@
       <c r="AC204" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD204" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE204" s="5" t="s">
+      <c r="AD204" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE204" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF204" s="1" t="s">
@@ -28750,10 +28753,10 @@
       <c r="AC205" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD205" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE205" s="5" t="s">
+      <c r="AD205" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE205" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF205" s="1" t="s">
@@ -28857,10 +28860,10 @@
       <c r="AC206" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD206" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE206" s="5" t="s">
+      <c r="AD206" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE206" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF206" s="1" t="s">
@@ -28964,10 +28967,10 @@
       <c r="AC207" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD207" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE207" s="5" t="s">
+      <c r="AD207" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE207" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF207" s="1" t="s">
@@ -29071,10 +29074,10 @@
       <c r="AC208" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD208" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE208" s="5" t="s">
+      <c r="AD208" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE208" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF208" s="1" t="s">
@@ -29178,10 +29181,10 @@
       <c r="AC209" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD209" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE209" s="5" t="s">
+      <c r="AD209" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE209" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF209" s="1" t="s">
@@ -29285,10 +29288,10 @@
       <c r="AC210" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD210" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE210" s="5" t="s">
+      <c r="AD210" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE210" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF210" s="1" t="s">
@@ -29392,10 +29395,10 @@
       <c r="AC211" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD211" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE211" s="5" t="s">
+      <c r="AD211" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE211" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF211" s="1" t="s">
@@ -29499,10 +29502,10 @@
       <c r="AC212" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD212" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE212" s="5" t="s">
+      <c r="AD212" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE212" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF212" s="1" t="s">
@@ -29606,10 +29609,10 @@
       <c r="AC213" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD213" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE213" s="5" t="s">
+      <c r="AD213" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE213" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF213" s="1" t="s">
@@ -29713,10 +29716,10 @@
       <c r="AC214" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD214" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE214" s="5" t="s">
+      <c r="AD214" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE214" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF214" s="1" t="s">
@@ -29820,10 +29823,10 @@
       <c r="AC215" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD215" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE215" s="5" t="s">
+      <c r="AD215" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE215" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF215" s="1" t="s">
@@ -29927,10 +29930,10 @@
       <c r="AC216" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD216" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE216" s="5" t="s">
+      <c r="AD216" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE216" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF216" s="1" t="s">
@@ -30034,10 +30037,10 @@
       <c r="AC217" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD217" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE217" s="5" t="s">
+      <c r="AD217" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE217" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF217" s="1" t="s">
@@ -30141,10 +30144,10 @@
       <c r="AC218" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD218" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE218" s="5" t="s">
+      <c r="AD218" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE218" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF218" s="1" t="s">
@@ -30248,10 +30251,10 @@
       <c r="AC219" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD219" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE219" s="5" t="s">
+      <c r="AD219" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE219" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF219" s="1" t="s">
@@ -30355,10 +30358,10 @@
       <c r="AC220" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD220" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE220" s="5" t="s">
+      <c r="AD220" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE220" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF220" s="1" t="s">
@@ -30462,10 +30465,10 @@
       <c r="AC221" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD221" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE221" s="5" t="s">
+      <c r="AD221" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE221" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF221" s="1" t="s">
@@ -30569,10 +30572,10 @@
       <c r="AC222" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD222" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE222" s="5" t="s">
+      <c r="AD222" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE222" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF222" s="1" t="s">
@@ -30676,10 +30679,10 @@
       <c r="AC223" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD223" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE223" s="5" t="s">
+      <c r="AD223" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE223" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF223" s="1" t="s">
@@ -30783,10 +30786,10 @@
       <c r="AC224" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD224" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE224" s="5" t="s">
+      <c r="AD224" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE224" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF224" s="1" t="s">
@@ -30890,10 +30893,10 @@
       <c r="AC225" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD225" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE225" s="5" t="s">
+      <c r="AD225" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE225" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF225" s="1" t="s">
@@ -30997,10 +31000,10 @@
       <c r="AC226" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD226" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE226" s="5" t="s">
+      <c r="AD226" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE226" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF226" s="1" t="s">
@@ -31104,10 +31107,10 @@
       <c r="AC227" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD227" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE227" s="5" t="s">
+      <c r="AD227" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE227" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF227" s="1" t="s">
@@ -31211,10 +31214,10 @@
       <c r="AC228" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD228" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE228" s="5" t="s">
+      <c r="AD228" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE228" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF228" s="1" t="s">
@@ -31318,10 +31321,10 @@
       <c r="AC229" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD229" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE229" s="5" t="s">
+      <c r="AD229" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE229" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF229" s="1" t="s">
@@ -31425,10 +31428,10 @@
       <c r="AC230" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD230" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE230" s="5" t="s">
+      <c r="AD230" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE230" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF230" s="1" t="s">
@@ -31532,10 +31535,10 @@
       <c r="AC231" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD231" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE231" s="5" t="s">
+      <c r="AD231" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE231" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF231" s="1" t="s">
@@ -31639,10 +31642,10 @@
       <c r="AC232" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD232" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE232" s="5" t="s">
+      <c r="AD232" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE232" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF232" s="1" t="s">
@@ -31746,10 +31749,10 @@
       <c r="AC233" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD233" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE233" s="5" t="s">
+      <c r="AD233" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE233" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF233" s="1" t="s">
@@ -31853,10 +31856,10 @@
       <c r="AC234" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD234" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE234" s="5" t="s">
+      <c r="AD234" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE234" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF234" s="1" t="s">
@@ -31960,10 +31963,10 @@
       <c r="AC235" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD235" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE235" s="5" t="s">
+      <c r="AD235" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE235" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF235" s="1" t="s">
@@ -32067,10 +32070,10 @@
       <c r="AC236" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD236" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE236" s="5" t="s">
+      <c r="AD236" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE236" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF236" s="1" t="s">
@@ -32174,10 +32177,10 @@
       <c r="AC237" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD237" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE237" s="5" t="s">
+      <c r="AD237" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE237" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF237" s="1" t="s">
@@ -32281,10 +32284,10 @@
       <c r="AC238" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD238" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE238" s="5" t="s">
+      <c r="AD238" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE238" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF238" s="1" t="s">
@@ -32388,10 +32391,10 @@
       <c r="AC239" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD239" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE239" s="5" t="s">
+      <c r="AD239" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE239" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF239" s="1" t="s">
@@ -32495,10 +32498,10 @@
       <c r="AC240" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD240" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE240" s="5" t="s">
+      <c r="AD240" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE240" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF240" s="1" t="s">
@@ -32602,10 +32605,10 @@
       <c r="AC241" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD241" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE241" s="5" t="s">
+      <c r="AD241" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE241" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF241" s="1" t="s">
@@ -32709,10 +32712,10 @@
       <c r="AC242" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD242" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE242" s="5" t="s">
+      <c r="AD242" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE242" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF242" s="1" t="s">
@@ -32816,10 +32819,10 @@
       <c r="AC243" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD243" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE243" s="5" t="s">
+      <c r="AD243" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE243" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF243" s="1" t="s">
@@ -32923,10 +32926,10 @@
       <c r="AC244" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD244" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE244" s="5" t="s">
+      <c r="AD244" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE244" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF244" s="1" t="s">
@@ -33030,10 +33033,10 @@
       <c r="AC245" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD245" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE245" s="5" t="s">
+      <c r="AD245" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE245" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF245" s="1" t="s">
@@ -33137,10 +33140,10 @@
       <c r="AC246" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD246" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE246" s="5" t="s">
+      <c r="AD246" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE246" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF246" s="1" t="s">
@@ -33244,10 +33247,10 @@
       <c r="AC247" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD247" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE247" s="5" t="s">
+      <c r="AD247" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE247" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF247" s="1" t="s">
@@ -33351,10 +33354,10 @@
       <c r="AC248" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD248" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE248" s="5" t="s">
+      <c r="AD248" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE248" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF248" s="1" t="s">
@@ -33458,10 +33461,10 @@
       <c r="AC249" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD249" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE249" s="5" t="s">
+      <c r="AD249" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE249" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF249" s="1" t="s">
@@ -33565,10 +33568,10 @@
       <c r="AC250" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD250" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE250" s="5" t="s">
+      <c r="AD250" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE250" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF250" s="1" t="s">
@@ -33672,10 +33675,10 @@
       <c r="AC251" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD251" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE251" s="5" t="s">
+      <c r="AD251" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE251" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF251" s="1" t="s">
@@ -33779,10 +33782,10 @@
       <c r="AC252" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD252" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE252" s="5" t="s">
+      <c r="AD252" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE252" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF252" s="1" t="s">
@@ -33886,10 +33889,10 @@
       <c r="AC253" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD253" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE253" s="5" t="s">
+      <c r="AD253" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE253" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF253" s="1" t="s">
@@ -33993,10 +33996,10 @@
       <c r="AC254" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD254" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE254" s="5" t="s">
+      <c r="AD254" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE254" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF254" s="1" t="s">
@@ -34100,10 +34103,10 @@
       <c r="AC255" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD255" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE255" s="5" t="s">
+      <c r="AD255" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE255" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF255" s="1" t="s">
@@ -34207,10 +34210,10 @@
       <c r="AC256" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD256" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE256" s="5" t="s">
+      <c r="AD256" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE256" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF256" s="1" t="s">
@@ -34314,10 +34317,10 @@
       <c r="AC257" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD257" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE257" s="5" t="s">
+      <c r="AD257" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE257" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF257" s="1" t="s">
@@ -34421,10 +34424,10 @@
       <c r="AC258" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD258" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE258" s="5" t="s">
+      <c r="AD258" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE258" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF258" s="1" t="s">
@@ -34528,10 +34531,10 @@
       <c r="AC259" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD259" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE259" s="5" t="s">
+      <c r="AD259" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE259" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF259" s="1" t="s">
@@ -34635,10 +34638,10 @@
       <c r="AC260" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD260" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE260" s="5" t="s">
+      <c r="AD260" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE260" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF260" s="1" t="s">
@@ -34742,10 +34745,10 @@
       <c r="AC261" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD261" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE261" s="5" t="s">
+      <c r="AD261" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE261" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF261" s="1" t="s">
@@ -34849,10 +34852,10 @@
       <c r="AC262" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD262" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE262" s="5" t="s">
+      <c r="AD262" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE262" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF262" s="1" t="s">
@@ -34956,10 +34959,10 @@
       <c r="AC263" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD263" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE263" s="5" t="s">
+      <c r="AD263" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE263" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF263" s="1" t="s">
@@ -35063,10 +35066,10 @@
       <c r="AC264" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD264" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE264" s="5" t="s">
+      <c r="AD264" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE264" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF264" s="1" t="s">
@@ -35170,10 +35173,10 @@
       <c r="AC265" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD265" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE265" s="5" t="s">
+      <c r="AD265" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE265" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF265" s="1" t="s">
@@ -35277,10 +35280,10 @@
       <c r="AC266" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD266" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE266" s="5" t="s">
+      <c r="AD266" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE266" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF266" s="1" t="s">
@@ -35384,10 +35387,10 @@
       <c r="AC267" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD267" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE267" s="5" t="s">
+      <c r="AD267" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE267" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF267" s="1" t="s">
@@ -35491,10 +35494,10 @@
       <c r="AC268" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD268" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE268" s="5" t="s">
+      <c r="AD268" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE268" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF268" s="1" t="s">
@@ -35598,10 +35601,10 @@
       <c r="AC269" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD269" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE269" s="5" t="s">
+      <c r="AD269" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE269" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF269" s="1" t="s">
@@ -35705,10 +35708,10 @@
       <c r="AC270" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD270" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE270" s="5" t="s">
+      <c r="AD270" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE270" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF270" s="1" t="s">
@@ -35812,10 +35815,10 @@
       <c r="AC271" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD271" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE271" s="5" t="s">
+      <c r="AD271" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE271" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF271" s="1" t="s">
@@ -35919,10 +35922,10 @@
       <c r="AC272" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD272" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE272" s="5" t="s">
+      <c r="AD272" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE272" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF272" s="1" t="s">
@@ -36026,10 +36029,10 @@
       <c r="AC273" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD273" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE273" s="5" t="s">
+      <c r="AD273" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE273" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF273" s="1" t="s">
@@ -36133,10 +36136,10 @@
       <c r="AC274" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD274" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE274" s="5" t="s">
+      <c r="AD274" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE274" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF274" s="1" t="s">
@@ -36240,10 +36243,10 @@
       <c r="AC275" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD275" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE275" s="5" t="s">
+      <c r="AD275" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE275" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF275" s="1" t="s">
@@ -36347,10 +36350,10 @@
       <c r="AC276" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD276" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE276" s="5" t="s">
+      <c r="AD276" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE276" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF276" s="1" t="s">
@@ -36454,10 +36457,10 @@
       <c r="AC277" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD277" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE277" s="5" t="s">
+      <c r="AD277" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE277" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF277" s="1" t="s">
@@ -36561,10 +36564,10 @@
       <c r="AC278" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD278" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE278" s="5" t="s">
+      <c r="AD278" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE278" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF278" s="1" t="s">
@@ -36668,10 +36671,10 @@
       <c r="AC279" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD279" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE279" s="5" t="s">
+      <c r="AD279" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE279" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF279" s="1" t="s">
@@ -36775,10 +36778,10 @@
       <c r="AC280" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD280" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE280" s="5" t="s">
+      <c r="AD280" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE280" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF280" s="1" t="s">
@@ -36882,10 +36885,10 @@
       <c r="AC281" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD281" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE281" s="5" t="s">
+      <c r="AD281" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE281" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF281" s="1" t="s">
@@ -36989,10 +36992,10 @@
       <c r="AC282" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD282" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE282" s="5" t="s">
+      <c r="AD282" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE282" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF282" s="1" t="s">
@@ -37096,10 +37099,10 @@
       <c r="AC283" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD283" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE283" s="5" t="s">
+      <c r="AD283" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE283" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF283" s="1" t="s">
@@ -37203,10 +37206,10 @@
       <c r="AC284" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD284" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE284" s="5" t="s">
+      <c r="AD284" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE284" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF284" s="1" t="s">
@@ -37310,10 +37313,10 @@
       <c r="AC285" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD285" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE285" s="5" t="s">
+      <c r="AD285" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE285" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF285" s="1" t="s">
@@ -37417,10 +37420,10 @@
       <c r="AC286" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD286" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE286" s="5" t="s">
+      <c r="AD286" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE286" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF286" s="1" t="s">
@@ -37524,10 +37527,10 @@
       <c r="AC287" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD287" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE287" s="5" t="s">
+      <c r="AD287" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE287" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF287" s="1" t="s">
@@ -37631,10 +37634,10 @@
       <c r="AC288" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD288" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE288" s="5" t="s">
+      <c r="AD288" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE288" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF288" s="1" t="s">
@@ -37738,10 +37741,10 @@
       <c r="AC289" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD289" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE289" s="5" t="s">
+      <c r="AD289" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE289" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF289" s="1" t="s">
@@ -37845,10 +37848,10 @@
       <c r="AC290" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD290" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE290" s="5" t="s">
+      <c r="AD290" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE290" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF290" s="1" t="s">
@@ -37952,10 +37955,10 @@
       <c r="AC291" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD291" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE291" s="5" t="s">
+      <c r="AD291" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE291" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF291" s="1" t="s">
@@ -38059,10 +38062,10 @@
       <c r="AC292" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD292" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE292" s="5" t="s">
+      <c r="AD292" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE292" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF292" s="1" t="s">
@@ -38166,10 +38169,10 @@
       <c r="AC293" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD293" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE293" s="5" t="s">
+      <c r="AD293" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE293" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF293" s="1" t="s">
@@ -38273,10 +38276,10 @@
       <c r="AC294" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD294" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE294" s="5" t="s">
+      <c r="AD294" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE294" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF294" s="1" t="s">
@@ -38380,10 +38383,10 @@
       <c r="AC295" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD295" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE295" s="5" t="s">
+      <c r="AD295" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE295" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF295" s="1" t="s">
@@ -38487,10 +38490,10 @@
       <c r="AC296" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD296" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE296" s="5" t="s">
+      <c r="AD296" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE296" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF296" s="1" t="s">
@@ -38594,10 +38597,10 @@
       <c r="AC297" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD297" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE297" s="5" t="s">
+      <c r="AD297" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE297" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF297" s="1" t="s">
@@ -38701,10 +38704,10 @@
       <c r="AC298" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD298" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE298" s="5" t="s">
+      <c r="AD298" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE298" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF298" s="1" t="s">
@@ -38808,10 +38811,10 @@
       <c r="AC299" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD299" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE299" s="5" t="s">
+      <c r="AD299" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE299" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF299" s="1" t="s">
@@ -38915,10 +38918,10 @@
       <c r="AC300" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD300" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE300" s="5" t="s">
+      <c r="AD300" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE300" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF300" s="1" t="s">
@@ -39022,10 +39025,10 @@
       <c r="AC301" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD301" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE301" s="5" t="s">
+      <c r="AD301" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE301" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF301" s="1" t="s">
@@ -39129,10 +39132,10 @@
       <c r="AC302" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD302" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE302" s="5" t="s">
+      <c r="AD302" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE302" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF302" s="1" t="s">
@@ -39236,10 +39239,10 @@
       <c r="AC303" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD303" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE303" s="5" t="s">
+      <c r="AD303" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE303" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF303" s="1" t="s">
@@ -39343,10 +39346,10 @@
       <c r="AC304" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD304" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE304" s="5" t="s">
+      <c r="AD304" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE304" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF304" s="1" t="s">
@@ -39450,10 +39453,10 @@
       <c r="AC305" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD305" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE305" s="5" t="s">
+      <c r="AD305" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE305" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF305" s="1" t="s">
@@ -39557,10 +39560,10 @@
       <c r="AC306" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD306" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE306" s="5" t="s">
+      <c r="AD306" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE306" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF306" s="1" t="s">
@@ -39664,10 +39667,10 @@
       <c r="AC307" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD307" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE307" s="5" t="s">
+      <c r="AD307" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE307" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF307" s="1" t="s">
@@ -39771,10 +39774,10 @@
       <c r="AC308" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD308" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE308" s="5" t="s">
+      <c r="AD308" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE308" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF308" s="1" t="s">
@@ -39878,10 +39881,10 @@
       <c r="AC309" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD309" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE309" s="5" t="s">
+      <c r="AD309" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE309" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF309" s="1" t="s">
@@ -39985,10 +39988,10 @@
       <c r="AC310" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD310" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE310" s="5" t="s">
+      <c r="AD310" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE310" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF310" s="1" t="s">
@@ -40092,10 +40095,10 @@
       <c r="AC311" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD311" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE311" s="5" t="s">
+      <c r="AD311" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE311" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF311" s="1" t="s">
@@ -40199,10 +40202,10 @@
       <c r="AC312" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD312" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE312" s="5" t="s">
+      <c r="AD312" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE312" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF312" s="1" t="s">
@@ -40306,10 +40309,10 @@
       <c r="AC313" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD313" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE313" s="5" t="s">
+      <c r="AD313" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE313" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF313" s="1" t="s">
@@ -40413,10 +40416,10 @@
       <c r="AC314" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD314" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE314" s="5" t="s">
+      <c r="AD314" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE314" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF314" s="1" t="s">
@@ -40520,10 +40523,10 @@
       <c r="AC315" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD315" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE315" s="5" t="s">
+      <c r="AD315" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE315" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF315" s="1" t="s">
@@ -40627,10 +40630,10 @@
       <c r="AC316" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD316" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE316" s="5" t="s">
+      <c r="AD316" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE316" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF316" s="1" t="s">
@@ -40734,10 +40737,10 @@
       <c r="AC317" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD317" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE317" s="5" t="s">
+      <c r="AD317" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE317" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF317" s="1" t="s">
@@ -40841,10 +40844,10 @@
       <c r="AC318" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD318" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE318" s="5" t="s">
+      <c r="AD318" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE318" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF318" s="1" t="s">
@@ -40948,10 +40951,10 @@
       <c r="AC319" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD319" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE319" s="5" t="s">
+      <c r="AD319" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE319" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF319" s="1" t="s">
@@ -41055,10 +41058,10 @@
       <c r="AC320" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD320" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE320" s="5" t="s">
+      <c r="AD320" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE320" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF320" s="1" t="s">
@@ -41162,10 +41165,10 @@
       <c r="AC321" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD321" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE321" s="5" t="s">
+      <c r="AD321" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE321" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF321" s="1" t="s">
@@ -41269,10 +41272,10 @@
       <c r="AC322" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD322" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE322" s="5" t="s">
+      <c r="AD322" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE322" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF322" s="1" t="s">
@@ -41376,10 +41379,10 @@
       <c r="AC323" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD323" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE323" s="5" t="s">
+      <c r="AD323" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE323" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF323" s="1" t="s">
@@ -41483,10 +41486,10 @@
       <c r="AC324" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD324" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE324" s="5" t="s">
+      <c r="AD324" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE324" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF324" s="1" t="s">
@@ -41590,10 +41593,10 @@
       <c r="AC325" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD325" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE325" s="5" t="s">
+      <c r="AD325" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE325" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF325" s="1" t="s">
@@ -41697,10 +41700,10 @@
       <c r="AC326" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD326" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE326" s="5" t="s">
+      <c r="AD326" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE326" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF326" s="1" t="s">
@@ -41804,10 +41807,10 @@
       <c r="AC327" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD327" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE327" s="5" t="s">
+      <c r="AD327" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE327" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF327" s="1" t="s">
@@ -41911,10 +41914,10 @@
       <c r="AC328" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD328" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE328" s="5" t="s">
+      <c r="AD328" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE328" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF328" s="1" t="s">
@@ -42018,10 +42021,10 @@
       <c r="AC329" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD329" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE329" s="5" t="s">
+      <c r="AD329" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE329" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF329" s="1" t="s">
@@ -42125,10 +42128,10 @@
       <c r="AC330" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD330" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE330" s="5" t="s">
+      <c r="AD330" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE330" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF330" s="1" t="s">
@@ -42232,10 +42235,10 @@
       <c r="AC331" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD331" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE331" s="5" t="s">
+      <c r="AD331" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE331" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF331" s="1" t="s">
@@ -42339,10 +42342,10 @@
       <c r="AC332" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD332" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE332" s="5" t="s">
+      <c r="AD332" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE332" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF332" s="1" t="s">
@@ -42446,10 +42449,10 @@
       <c r="AC333" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD333" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE333" s="5" t="s">
+      <c r="AD333" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE333" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF333" s="1" t="s">
@@ -42553,10 +42556,10 @@
       <c r="AC334" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD334" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE334" s="5" t="s">
+      <c r="AD334" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE334" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF334" s="1" t="s">
@@ -42660,10 +42663,10 @@
       <c r="AC335" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD335" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE335" s="5" t="s">
+      <c r="AD335" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE335" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF335" s="1" t="s">
@@ -42767,10 +42770,10 @@
       <c r="AC336" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD336" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE336" s="5" t="s">
+      <c r="AD336" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE336" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF336" s="1" t="s">
@@ -42874,10 +42877,10 @@
       <c r="AC337" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD337" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE337" s="5" t="s">
+      <c r="AD337" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE337" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF337" s="1" t="s">
@@ -42981,10 +42984,10 @@
       <c r="AC338" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD338" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE338" s="5" t="s">
+      <c r="AD338" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE338" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF338" s="1" t="s">
@@ -43088,10 +43091,10 @@
       <c r="AC339" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD339" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE339" s="5" t="s">
+      <c r="AD339" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE339" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF339" s="1" t="s">
@@ -43195,10 +43198,10 @@
       <c r="AC340" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD340" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE340" s="5" t="s">
+      <c r="AD340" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE340" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF340" s="1" t="s">
@@ -43302,10 +43305,10 @@
       <c r="AC341" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD341" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE341" s="5" t="s">
+      <c r="AD341" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE341" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF341" s="1" t="s">
@@ -43409,10 +43412,10 @@
       <c r="AC342" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD342" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE342" s="5" t="s">
+      <c r="AD342" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE342" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF342" s="1" t="s">
@@ -43516,10 +43519,10 @@
       <c r="AC343" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD343" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE343" s="5" t="s">
+      <c r="AD343" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE343" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF343" s="1" t="s">
@@ -43623,10 +43626,10 @@
       <c r="AC344" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD344" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE344" s="5" t="s">
+      <c r="AD344" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE344" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF344" s="1" t="s">
@@ -43730,10 +43733,10 @@
       <c r="AC345" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD345" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE345" s="5" t="s">
+      <c r="AD345" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE345" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF345" s="1" t="s">
@@ -43837,10 +43840,10 @@
       <c r="AC346" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD346" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE346" s="5" t="s">
+      <c r="AD346" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE346" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF346" s="1" t="s">
@@ -43944,10 +43947,10 @@
       <c r="AC347" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD347" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE347" s="5" t="s">
+      <c r="AD347" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE347" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF347" s="1" t="s">
@@ -44051,10 +44054,10 @@
       <c r="AC348" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD348" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE348" s="5" t="s">
+      <c r="AD348" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE348" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF348" s="1" t="s">
@@ -44158,10 +44161,10 @@
       <c r="AC349" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD349" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE349" s="5" t="s">
+      <c r="AD349" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE349" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF349" s="1" t="s">
@@ -44265,10 +44268,10 @@
       <c r="AC350" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD350" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE350" s="5" t="s">
+      <c r="AD350" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE350" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF350" s="1" t="s">
@@ -44372,10 +44375,10 @@
       <c r="AC351" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD351" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE351" s="5" t="s">
+      <c r="AD351" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE351" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF351" s="1" t="s">
@@ -44479,10 +44482,10 @@
       <c r="AC352" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD352" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE352" s="5" t="s">
+      <c r="AD352" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE352" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF352" s="1" t="s">
@@ -44586,10 +44589,10 @@
       <c r="AC353" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD353" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE353" s="5" t="s">
+      <c r="AD353" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE353" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF353" s="1" t="s">
@@ -44693,10 +44696,10 @@
       <c r="AC354" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD354" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE354" s="5" t="s">
+      <c r="AD354" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE354" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF354" s="1" t="s">
@@ -44800,10 +44803,10 @@
       <c r="AC355" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD355" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE355" s="5" t="s">
+      <c r="AD355" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE355" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF355" s="1" t="s">
@@ -44907,10 +44910,10 @@
       <c r="AC356" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD356" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE356" s="5" t="s">
+      <c r="AD356" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE356" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF356" s="1" t="s">
@@ -45014,10 +45017,10 @@
       <c r="AC357" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD357" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE357" s="5" t="s">
+      <c r="AD357" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE357" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF357" s="1" t="s">
@@ -45121,10 +45124,10 @@
       <c r="AC358" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD358" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE358" s="5" t="s">
+      <c r="AD358" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE358" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF358" s="1" t="s">
@@ -45228,10 +45231,10 @@
       <c r="AC359" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD359" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE359" s="5" t="s">
+      <c r="AD359" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE359" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF359" s="1" t="s">
@@ -45335,10 +45338,10 @@
       <c r="AC360" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD360" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE360" s="5" t="s">
+      <c r="AD360" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE360" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF360" s="1" t="s">
@@ -45442,10 +45445,10 @@
       <c r="AC361" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD361" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE361" s="5" t="s">
+      <c r="AD361" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE361" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF361" s="1" t="s">
@@ -45549,10 +45552,10 @@
       <c r="AC362" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD362" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE362" s="5" t="s">
+      <c r="AD362" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE362" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF362" s="1" t="s">
@@ -45656,10 +45659,10 @@
       <c r="AC363" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD363" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE363" s="5" t="s">
+      <c r="AD363" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE363" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF363" s="1" t="s">
@@ -45763,10 +45766,10 @@
       <c r="AC364" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD364" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE364" s="5" t="s">
+      <c r="AD364" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE364" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF364" s="1" t="s">
@@ -45870,10 +45873,10 @@
       <c r="AC365" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD365" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE365" s="5" t="s">
+      <c r="AD365" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE365" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF365" s="1" t="s">
@@ -45977,10 +45980,10 @@
       <c r="AC366" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD366" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE366" s="5" t="s">
+      <c r="AD366" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE366" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF366" s="1" t="s">
@@ -46084,10 +46087,10 @@
       <c r="AC367" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD367" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE367" s="5" t="s">
+      <c r="AD367" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE367" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF367" s="1" t="s">
@@ -46191,10 +46194,10 @@
       <c r="AC368" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD368" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE368" s="5" t="s">
+      <c r="AD368" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE368" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF368" s="1" t="s">
@@ -46298,10 +46301,10 @@
       <c r="AC369" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD369" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE369" s="5" t="s">
+      <c r="AD369" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE369" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF369" s="1" t="s">
@@ -46405,10 +46408,10 @@
       <c r="AC370" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD370" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE370" s="5" t="s">
+      <c r="AD370" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE370" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF370" s="1" t="s">
@@ -46512,10 +46515,10 @@
       <c r="AC371" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD371" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE371" s="5" t="s">
+      <c r="AD371" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE371" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF371" s="1" t="s">
@@ -46619,10 +46622,10 @@
       <c r="AC372" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD372" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE372" s="5" t="s">
+      <c r="AD372" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE372" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF372" s="1" t="s">
@@ -46726,10 +46729,10 @@
       <c r="AC373" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD373" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE373" s="5" t="s">
+      <c r="AD373" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE373" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF373" s="1" t="s">
@@ -46833,10 +46836,10 @@
       <c r="AC374" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD374" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE374" s="5" t="s">
+      <c r="AD374" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE374" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF374" s="1" t="s">
@@ -46940,10 +46943,10 @@
       <c r="AC375" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD375" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE375" s="5" t="s">
+      <c r="AD375" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE375" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF375" s="1" t="s">
@@ -47047,10 +47050,10 @@
       <c r="AC376" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD376" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE376" s="5" t="s">
+      <c r="AD376" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE376" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF376" s="1" t="s">
@@ -47154,10 +47157,10 @@
       <c r="AC377" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD377" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE377" s="5" t="s">
+      <c r="AD377" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE377" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF377" s="1" t="s">
@@ -47261,10 +47264,10 @@
       <c r="AC378" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD378" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE378" s="5" t="s">
+      <c r="AD378" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE378" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF378" s="1" t="s">
@@ -47368,10 +47371,10 @@
       <c r="AC379" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD379" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE379" s="5" t="s">
+      <c r="AD379" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE379" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF379" s="1" t="s">
@@ -47475,10 +47478,10 @@
       <c r="AC380" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD380" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE380" s="5" t="s">
+      <c r="AD380" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE380" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF380" s="1" t="s">
@@ -47582,10 +47585,10 @@
       <c r="AC381" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD381" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE381" s="5" t="s">
+      <c r="AD381" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE381" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF381" s="1" t="s">
@@ -47689,10 +47692,10 @@
       <c r="AC382" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD382" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE382" s="5" t="s">
+      <c r="AD382" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE382" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF382" s="1" t="s">
@@ -47796,10 +47799,10 @@
       <c r="AC383" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD383" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE383" s="5" t="s">
+      <c r="AD383" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE383" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF383" s="1" t="s">
@@ -47903,10 +47906,10 @@
       <c r="AC384" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD384" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE384" s="5" t="s">
+      <c r="AD384" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE384" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF384" s="1" t="s">
@@ -48010,10 +48013,10 @@
       <c r="AC385" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD385" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE385" s="5" t="s">
+      <c r="AD385" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE385" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF385" s="1" t="s">
@@ -48117,10 +48120,10 @@
       <c r="AC386" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD386" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE386" s="5" t="s">
+      <c r="AD386" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE386" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF386" s="1" t="s">
@@ -48224,10 +48227,10 @@
       <c r="AC387" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD387" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE387" s="5" t="s">
+      <c r="AD387" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE387" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF387" s="1" t="s">
@@ -48331,10 +48334,10 @@
       <c r="AC388" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD388" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE388" s="5" t="s">
+      <c r="AD388" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE388" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF388" s="1" t="s">
@@ -48438,10 +48441,10 @@
       <c r="AC389" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD389" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE389" s="5" t="s">
+      <c r="AD389" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE389" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF389" s="1" t="s">
@@ -48545,10 +48548,10 @@
       <c r="AC390" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD390" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE390" s="5" t="s">
+      <c r="AD390" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE390" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF390" s="1" t="s">
@@ -48652,10 +48655,10 @@
       <c r="AC391" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD391" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE391" s="5" t="s">
+      <c r="AD391" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE391" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF391" s="1" t="s">
@@ -48759,10 +48762,10 @@
       <c r="AC392" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD392" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE392" s="5" t="s">
+      <c r="AD392" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE392" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF392" s="1" t="s">
@@ -48866,10 +48869,10 @@
       <c r="AC393" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD393" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE393" s="5" t="s">
+      <c r="AD393" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE393" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF393" s="1" t="s">
@@ -48973,10 +48976,10 @@
       <c r="AC394" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD394" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE394" s="5" t="s">
+      <c r="AD394" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE394" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF394" s="1" t="s">
@@ -49080,10 +49083,10 @@
       <c r="AC395" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD395" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE395" s="5" t="s">
+      <c r="AD395" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE395" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF395" s="1" t="s">
@@ -49187,10 +49190,10 @@
       <c r="AC396" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD396" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE396" s="5" t="s">
+      <c r="AD396" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE396" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF396" s="1" t="s">
@@ -49294,10 +49297,10 @@
       <c r="AC397" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD397" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE397" s="5" t="s">
+      <c r="AD397" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE397" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF397" s="1" t="s">
@@ -49401,10 +49404,10 @@
       <c r="AC398" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD398" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE398" s="5" t="s">
+      <c r="AD398" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE398" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF398" s="1" t="s">
@@ -49508,10 +49511,10 @@
       <c r="AC399" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD399" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE399" s="5" t="s">
+      <c r="AD399" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE399" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF399" s="1" t="s">
@@ -49615,10 +49618,10 @@
       <c r="AC400" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD400" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE400" s="5" t="s">
+      <c r="AD400" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE400" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF400" s="1" t="s">
@@ -49722,10 +49725,10 @@
       <c r="AC401" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD401" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE401" s="5" t="s">
+      <c r="AD401" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE401" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF401" s="1" t="s">
@@ -49829,10 +49832,10 @@
       <c r="AC402" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD402" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE402" s="5" t="s">
+      <c r="AD402" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE402" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF402" s="1" t="s">
@@ -49936,10 +49939,10 @@
       <c r="AC403" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD403" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE403" s="5" t="s">
+      <c r="AD403" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE403" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF403" s="1" t="s">
@@ -50043,10 +50046,10 @@
       <c r="AC404" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD404" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE404" s="5" t="s">
+      <c r="AD404" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE404" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF404" s="1" t="s">
@@ -50150,10 +50153,10 @@
       <c r="AC405" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD405" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE405" s="5" t="s">
+      <c r="AD405" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE405" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF405" s="1" t="s">
@@ -50257,10 +50260,10 @@
       <c r="AC406" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD406" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE406" s="5" t="s">
+      <c r="AD406" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE406" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF406" s="1" t="s">
@@ -50364,10 +50367,10 @@
       <c r="AC407" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD407" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE407" s="5" t="s">
+      <c r="AD407" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE407" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF407" s="1" t="s">
@@ -50471,10 +50474,10 @@
       <c r="AC408" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD408" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE408" s="5" t="s">
+      <c r="AD408" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE408" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF408" s="1" t="s">
@@ -50578,10 +50581,10 @@
       <c r="AC409" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD409" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE409" s="5" t="s">
+      <c r="AD409" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE409" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF409" s="1" t="s">
@@ -50685,10 +50688,10 @@
       <c r="AC410" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD410" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE410" s="5" t="s">
+      <c r="AD410" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE410" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF410" s="1" t="s">
@@ -50792,10 +50795,10 @@
       <c r="AC411" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD411" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE411" s="5" t="s">
+      <c r="AD411" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE411" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF411" s="1" t="s">
@@ -50899,10 +50902,10 @@
       <c r="AC412" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD412" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE412" s="5" t="s">
+      <c r="AD412" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE412" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF412" s="1" t="s">
@@ -51006,10 +51009,10 @@
       <c r="AC413" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD413" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE413" s="5" t="s">
+      <c r="AD413" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE413" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF413" s="1" t="s">
@@ -51113,10 +51116,10 @@
       <c r="AC414" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD414" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE414" s="5" t="s">
+      <c r="AD414" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE414" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF414" s="1" t="s">
@@ -51220,10 +51223,10 @@
       <c r="AC415" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD415" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE415" s="5" t="s">
+      <c r="AD415" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE415" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF415" s="1" t="s">
@@ -51327,10 +51330,10 @@
       <c r="AC416" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD416" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE416" s="5" t="s">
+      <c r="AD416" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE416" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF416" s="1" t="s">
@@ -51434,10 +51437,10 @@
       <c r="AC417" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD417" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE417" s="5" t="s">
+      <c r="AD417" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE417" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF417" s="1" t="s">
@@ -51541,10 +51544,10 @@
       <c r="AC418" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD418" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE418" s="5" t="s">
+      <c r="AD418" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE418" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF418" s="1" t="s">
@@ -51648,10 +51651,10 @@
       <c r="AC419" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD419" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE419" s="5" t="s">
+      <c r="AD419" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE419" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF419" s="1" t="s">
@@ -51755,10 +51758,10 @@
       <c r="AC420" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD420" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE420" s="5" t="s">
+      <c r="AD420" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE420" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF420" s="1" t="s">
@@ -51862,10 +51865,10 @@
       <c r="AC421" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD421" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE421" s="5" t="s">
+      <c r="AD421" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE421" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF421" s="1" t="s">
@@ -51969,10 +51972,10 @@
       <c r="AC422" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD422" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE422" s="5" t="s">
+      <c r="AD422" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE422" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF422" s="1" t="s">
@@ -52076,10 +52079,10 @@
       <c r="AC423" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD423" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE423" s="5" t="s">
+      <c r="AD423" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE423" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF423" s="1" t="s">
@@ -52183,10 +52186,10 @@
       <c r="AC424" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD424" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE424" s="5" t="s">
+      <c r="AD424" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE424" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF424" s="1" t="s">
@@ -52290,10 +52293,10 @@
       <c r="AC425" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD425" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE425" s="5" t="s">
+      <c r="AD425" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE425" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF425" s="1" t="s">
@@ -52397,10 +52400,10 @@
       <c r="AC426" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD426" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE426" s="5" t="s">
+      <c r="AD426" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE426" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF426" s="1" t="s">
@@ -52504,10 +52507,10 @@
       <c r="AC427" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD427" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE427" s="5" t="s">
+      <c r="AD427" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE427" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF427" s="1" t="s">
@@ -52611,10 +52614,10 @@
       <c r="AC428" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD428" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE428" s="5" t="s">
+      <c r="AD428" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE428" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF428" s="1" t="s">
@@ -52718,10 +52721,10 @@
       <c r="AC429" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD429" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE429" s="5" t="s">
+      <c r="AD429" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE429" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF429" s="1" t="s">
@@ -52825,10 +52828,10 @@
       <c r="AC430" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD430" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE430" s="5" t="s">
+      <c r="AD430" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE430" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF430" s="1" t="s">
@@ -52932,10 +52935,10 @@
       <c r="AC431" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD431" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE431" s="5" t="s">
+      <c r="AD431" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE431" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF431" s="1" t="s">
@@ -53039,10 +53042,10 @@
       <c r="AC432" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD432" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE432" s="5" t="s">
+      <c r="AD432" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE432" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF432" s="1" t="s">
@@ -53146,10 +53149,10 @@
       <c r="AC433" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD433" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE433" s="5" t="s">
+      <c r="AD433" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE433" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF433" s="1" t="s">
@@ -53253,10 +53256,10 @@
       <c r="AC434" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD434" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE434" s="5" t="s">
+      <c r="AD434" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE434" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF434" s="1" t="s">
@@ -53360,10 +53363,10 @@
       <c r="AC435" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD435" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE435" s="5" t="s">
+      <c r="AD435" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE435" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF435" s="1" t="s">
@@ -53467,10 +53470,10 @@
       <c r="AC436" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD436" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE436" s="5" t="s">
+      <c r="AD436" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE436" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF436" s="1" t="s">
@@ -53574,10 +53577,10 @@
       <c r="AC437" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD437" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE437" s="5" t="s">
+      <c r="AD437" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE437" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF437" s="1" t="s">
@@ -53681,10 +53684,10 @@
       <c r="AC438" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD438" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE438" s="5" t="s">
+      <c r="AD438" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE438" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF438" s="1" t="s">
@@ -53788,10 +53791,10 @@
       <c r="AC439" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD439" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE439" s="5" t="s">
+      <c r="AD439" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE439" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF439" s="1" t="s">
@@ -53895,10 +53898,10 @@
       <c r="AC440" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD440" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE440" s="5" t="s">
+      <c r="AD440" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE440" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF440" s="1" t="s">
@@ -54002,10 +54005,10 @@
       <c r="AC441" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD441" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE441" s="5" t="s">
+      <c r="AD441" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE441" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF441" s="1" t="s">
@@ -54109,10 +54112,10 @@
       <c r="AC442" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD442" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE442" s="5" t="s">
+      <c r="AD442" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE442" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF442" s="1" t="s">
@@ -54216,10 +54219,10 @@
       <c r="AC443" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD443" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE443" s="5" t="s">
+      <c r="AD443" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE443" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF443" s="1" t="s">
@@ -54323,10 +54326,10 @@
       <c r="AC444" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD444" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE444" s="5" t="s">
+      <c r="AD444" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE444" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF444" s="1" t="s">
@@ -54430,10 +54433,10 @@
       <c r="AC445" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD445" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE445" s="5" t="s">
+      <c r="AD445" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE445" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF445" s="1" t="s">
@@ -54537,10 +54540,10 @@
       <c r="AC446" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD446" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE446" s="5" t="s">
+      <c r="AD446" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE446" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF446" s="1" t="s">
@@ -54644,10 +54647,10 @@
       <c r="AC447" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD447" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE447" s="5" t="s">
+      <c r="AD447" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE447" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF447" s="1" t="s">
@@ -54751,10 +54754,10 @@
       <c r="AC448" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD448" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE448" s="5" t="s">
+      <c r="AD448" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE448" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF448" s="1" t="s">
@@ -54858,10 +54861,10 @@
       <c r="AC449" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD449" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE449" s="5" t="s">
+      <c r="AD449" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE449" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF449" s="1" t="s">
@@ -54965,10 +54968,10 @@
       <c r="AC450" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD450" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE450" s="5" t="s">
+      <c r="AD450" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE450" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF450" s="1" t="s">
@@ -55072,10 +55075,10 @@
       <c r="AC451" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD451" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE451" s="5" t="s">
+      <c r="AD451" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE451" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF451" s="1" t="s">
@@ -55179,10 +55182,10 @@
       <c r="AC452" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD452" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE452" s="5" t="s">
+      <c r="AD452" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE452" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF452" s="1" t="s">
@@ -55286,10 +55289,10 @@
       <c r="AC453" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD453" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE453" s="5" t="s">
+      <c r="AD453" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE453" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF453" s="1" t="s">
@@ -55393,10 +55396,10 @@
       <c r="AC454" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD454" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE454" s="5" t="s">
+      <c r="AD454" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE454" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF454" s="1" t="s">
@@ -55500,10 +55503,10 @@
       <c r="AC455" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD455" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE455" s="5" t="s">
+      <c r="AD455" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE455" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF455" s="1" t="s">
@@ -55607,10 +55610,10 @@
       <c r="AC456" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD456" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE456" s="5" t="s">
+      <c r="AD456" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE456" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF456" s="1" t="s">
@@ -55714,10 +55717,10 @@
       <c r="AC457" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD457" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE457" s="5" t="s">
+      <c r="AD457" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE457" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF457" s="1" t="s">
@@ -55821,10 +55824,10 @@
       <c r="AC458" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD458" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE458" s="5" t="s">
+      <c r="AD458" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE458" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF458" s="1" t="s">
@@ -55928,10 +55931,10 @@
       <c r="AC459" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD459" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE459" s="5" t="s">
+      <c r="AD459" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE459" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF459" s="1" t="s">
@@ -56035,10 +56038,10 @@
       <c r="AC460" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD460" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE460" s="5" t="s">
+      <c r="AD460" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE460" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF460" s="1" t="s">
@@ -56142,10 +56145,10 @@
       <c r="AC461" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD461" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE461" s="5" t="s">
+      <c r="AD461" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE461" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF461" s="1" t="s">
@@ -56249,10 +56252,10 @@
       <c r="AC462" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD462" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE462" s="5" t="s">
+      <c r="AD462" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE462" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF462" s="1" t="s">
@@ -56356,10 +56359,10 @@
       <c r="AC463" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD463" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE463" s="5" t="s">
+      <c r="AD463" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE463" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF463" s="1" t="s">
@@ -56463,10 +56466,10 @@
       <c r="AC464" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD464" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE464" s="5" t="s">
+      <c r="AD464" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE464" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF464" s="1" t="s">
@@ -56570,10 +56573,10 @@
       <c r="AC465" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD465" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE465" s="5" t="s">
+      <c r="AD465" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE465" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF465" s="1" t="s">
@@ -56677,10 +56680,10 @@
       <c r="AC466" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD466" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE466" s="5" t="s">
+      <c r="AD466" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE466" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF466" s="1" t="s">
@@ -56784,10 +56787,10 @@
       <c r="AC467" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD467" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE467" s="5" t="s">
+      <c r="AD467" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE467" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF467" s="1" t="s">
@@ -56891,10 +56894,10 @@
       <c r="AC468" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD468" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE468" s="5" t="s">
+      <c r="AD468" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE468" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF468" s="1" t="s">
@@ -56998,10 +57001,10 @@
       <c r="AC469" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD469" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE469" s="5" t="s">
+      <c r="AD469" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE469" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF469" s="1" t="s">
@@ -57105,10 +57108,10 @@
       <c r="AC470" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD470" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE470" s="5" t="s">
+      <c r="AD470" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE470" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF470" s="1" t="s">
@@ -57212,10 +57215,10 @@
       <c r="AC471" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD471" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE471" s="5" t="s">
+      <c r="AD471" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE471" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF471" s="1" t="s">
@@ -57319,10 +57322,10 @@
       <c r="AC472" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD472" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE472" s="5" t="s">
+      <c r="AD472" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE472" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF472" s="1" t="s">
@@ -57426,10 +57429,10 @@
       <c r="AC473" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD473" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE473" s="5" t="s">
+      <c r="AD473" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE473" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF473" s="1" t="s">
@@ -57533,10 +57536,10 @@
       <c r="AC474" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD474" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE474" s="5" t="s">
+      <c r="AD474" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE474" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF474" s="1" t="s">
@@ -57640,10 +57643,10 @@
       <c r="AC475" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD475" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE475" s="5" t="s">
+      <c r="AD475" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE475" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF475" s="1" t="s">
@@ -57747,10 +57750,10 @@
       <c r="AC476" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD476" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE476" s="5" t="s">
+      <c r="AD476" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE476" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF476" s="1" t="s">
@@ -57854,10 +57857,10 @@
       <c r="AC477" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD477" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE477" s="5" t="s">
+      <c r="AD477" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE477" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF477" s="1" t="s">
@@ -57961,10 +57964,10 @@
       <c r="AC478" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="AD478" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE478" s="5" t="s">
+      <c r="AD478" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE478" s="6" t="s">
         <v>63</v>
       </c>
       <c r="AF478" s="1" t="s">
@@ -59045,16 +59048,16 @@
       <c r="AF2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AG2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AH2" s="7" t="s">
+      <c r="AH2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AI2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="7" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>34</v>
       </c>
     </row>

--- a/medicamentos.xlsx
+++ b/medicamentos.xlsx
@@ -2316,7 +2316,7 @@
     <t>A02BA03</t>
   </si>
   <si>
-    <t>Imagens/Generic.webp</t>
+    <t>Imagens/MSRM.png</t>
   </si>
   <si>
     <t>Cytotec</t>
@@ -12661,7 +12661,7 @@
       <c r="AB54" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AC54" s="1" t="s">
+      <c r="AC54" s="15" t="s">
         <v>535</v>
       </c>
       <c r="AD54" s="7" t="s">
